--- a/outputs/488-14.xlsx
+++ b/outputs/488-14.xlsx
@@ -134,16 +134,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -429,11 +433,11 @@
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="16.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="16.72"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
@@ -884,11 +888,11 @@
   <dimension ref="A1:A85"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="20.14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
     </row>

--- a/outputs/488-14.xlsx
+++ b/outputs/488-14.xlsx
@@ -449,107 +449,107 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J4" s="1"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J5" s="1"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J6" s="1"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J7" s="1"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -569,17 +569,17 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -609,107 +609,107 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -734,132 +734,132 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
